--- a/Zeitplan Projekt 1.xlsx
+++ b/Zeitplan Projekt 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\4. ET\Projekte\Projekt 1-SmartGate Schleuse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAF4C5C-0C53-4C99-9BBD-0B69977C55D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3507131-047C-42CD-8733-50DA399B469C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="7200" yWindow="3795" windowWidth="21600" windowHeight="11295" xr2:uid="{5DC249E4-44FA-4F87-81C1-DF2CC93263BC}"/>
   </bookViews>
@@ -38,9 +38,24 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
+    <t>Projekt 1 : SmartGate-Schleuse</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>Oktober</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
     <t>Abgabe</t>
   </si>
   <si>
+    <t>Kalender Woche(KW)</t>
+  </si>
+  <si>
     <t>Analyse &amp; Definition</t>
   </si>
   <si>
@@ -86,19 +101,7 @@
     <t>- Dokumentation</t>
   </si>
   <si>
-    <t>September</t>
-  </si>
-  <si>
-    <t>Oktober</t>
-  </si>
-  <si>
-    <t>November</t>
-  </si>
-  <si>
-    <t>Kalender Woche(KW)</t>
-  </si>
-  <si>
-    <t>Projekt 1 : XXXX</t>
+    <t>- Programm</t>
   </si>
   <si>
     <t>Legende</t>
@@ -108,16 +111,13 @@
   </si>
   <si>
     <t>muss ich fertig sein</t>
-  </si>
-  <si>
-    <t>- Programm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,7 +155,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -182,18 +182,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -464,11 +458,104 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -489,9 +576,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -505,40 +589,55 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -547,10 +646,10 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -565,8 +664,9 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -585,7 +685,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -882,61 +982,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB7D85ED-FF04-404A-9E89-DD150ECAAADE}">
   <dimension ref="A1:N26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="14" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="39"/>
-    </row>
-    <row r="2" spans="1:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="25" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="43"/>
+    </row>
+    <row r="2" spans="1:14" ht="69.75" customHeight="1">
+      <c r="A2" s="47"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="24" t="s">
+        <v>4</v>
+      </c>
       <c r="E2" s="10"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="32"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="18" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>19</v>
+      <c r="F2" s="35"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="36"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="19" t="s">
+        <v>5</v>
       </c>
       <c r="B3" s="11">
         <v>36</v>
@@ -978,31 +1078,31 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="35"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="27"/>
+    <row r="4" spans="1:14">
+      <c r="A4" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="34"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="25"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="23"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="14"/>
       <c r="F5" s="13"/>
       <c r="G5" s="4"/>
@@ -1014,13 +1114,13 @@
       <c r="M5" s="4"/>
       <c r="N5" s="14"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>3</v>
+    <row r="6" spans="1:14">
+      <c r="A6" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="23"/>
+      <c r="D6" s="22"/>
       <c r="E6" s="14"/>
       <c r="F6" s="13"/>
       <c r="G6" s="4"/>
@@ -1032,13 +1132,13 @@
       <c r="M6" s="4"/>
       <c r="N6" s="14"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="48"/>
+    <row r="7" spans="1:14">
+      <c r="A7" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="30"/>
       <c r="C7" s="5"/>
-      <c r="D7" s="23"/>
+      <c r="D7" s="22"/>
       <c r="E7" s="14"/>
       <c r="F7" s="13"/>
       <c r="G7" s="4"/>
@@ -1050,13 +1150,13 @@
       <c r="M7" s="4"/>
       <c r="N7" s="14"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="27"/>
+    <row r="8" spans="1:14">
+      <c r="A8" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="25"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="23"/>
+      <c r="D8" s="22"/>
       <c r="E8" s="14"/>
       <c r="F8" s="13"/>
       <c r="G8" s="4"/>
@@ -1068,51 +1168,51 @@
       <c r="M8" s="4"/>
       <c r="N8" s="14"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="35"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="35"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>7</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="19"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="34"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="34"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="19" t="s">
+        <v>12</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="14"/>
-      <c r="F11" s="28"/>
+      <c r="F11" s="26"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="23"/>
+      <c r="H11" s="22"/>
       <c r="I11" s="4"/>
       <c r="J11" s="14"/>
       <c r="K11" s="9"/>
@@ -1120,17 +1220,17 @@
       <c r="M11" s="4"/>
       <c r="N11" s="14"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>8</v>
+    <row r="12" spans="1:14">
+      <c r="A12" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="14"/>
-      <c r="F12" s="28"/>
+      <c r="F12" s="26"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="23"/>
+      <c r="H12" s="22"/>
       <c r="I12" s="4"/>
       <c r="J12" s="14"/>
       <c r="K12" s="9"/>
@@ -1138,17 +1238,17 @@
       <c r="M12" s="4"/>
       <c r="N12" s="14"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>9</v>
+    <row r="13" spans="1:14">
+      <c r="A13" s="19" t="s">
+        <v>14</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="28"/>
+      <c r="F13" s="26"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="23"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="4"/>
       <c r="J13" s="14"/>
       <c r="K13" s="9"/>
@@ -1156,17 +1256,17 @@
       <c r="M13" s="4"/>
       <c r="N13" s="14"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>10</v>
+    <row r="14" spans="1:14">
+      <c r="A14" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="14"/>
-      <c r="F14" s="28"/>
+      <c r="F14" s="26"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="23"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="4"/>
       <c r="J14" s="14"/>
       <c r="K14" s="9"/>
@@ -1174,43 +1274,43 @@
       <c r="M14" s="4"/>
       <c r="N14" s="14"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="35"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="47"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
-        <v>12</v>
+    <row r="15" spans="1:14">
+      <c r="A15" s="19"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="34"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="53"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="4"/>
@@ -1222,13 +1322,13 @@
       <c r="I17" s="4"/>
       <c r="J17" s="14"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="49"/>
+      <c r="L17" s="27"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="19"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
-        <v>13</v>
+      <c r="N17" s="18"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="19" t="s">
+        <v>18</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="4"/>
@@ -1240,47 +1340,47 @@
       <c r="I18" s="4"/>
       <c r="J18" s="14"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="4"/>
+      <c r="L18" s="5"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="19"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="35"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="35"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
-        <v>15</v>
+      <c r="N18" s="18"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="19"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="34"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="32"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="34"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="19" t="s">
+        <v>20</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="4"/>
@@ -1291,14 +1391,14 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="14"/>
-      <c r="K21" s="9"/>
+      <c r="K21" s="28"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="29"/>
-    </row>
-    <row r="22" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
-        <v>24</v>
+      <c r="N21" s="44"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A22" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="16"/>
@@ -1309,26 +1409,26 @@
       <c r="H22" s="16"/>
       <c r="I22" s="16"/>
       <c r="J22" s="17"/>
-      <c r="K22" s="26"/>
+      <c r="K22" s="29"/>
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
-      <c r="N22" s="30"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="44"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N22" s="45"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="50"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" s="5"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14">
       <c r="A26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" s="7"/>
     </row>
@@ -1355,6 +1455,9 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K1:N1"/>
     <mergeCell ref="N21:N22"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="K20:N20"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="F10:J10"/>
@@ -1362,12 +1465,10 @@
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="F4:J4"/>
     <mergeCell ref="K4:N4"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="K20:N20"/>
   </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1501,36 +1602,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD0097F4-34EE-4FE3-A82B-F277A63EBBC5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD0097F4-34EE-4FE3-A82B-F277A63EBBC5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B4CF693-FC7B-4FDB-AAAD-F96D00643992}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f4aa2f46-1303-41ab-9828-3e8ca65a1acc"/>
-    <ds:schemaRef ds:uri="832c7e3d-e722-4221-b1bf-cd1e021cc1a2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B4CF693-FC7B-4FDB-AAAD-F96D00643992}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94677427-CEEE-4813-9DE3-FC15EDCEC7BA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94677427-CEEE-4813-9DE3-FC15EDCEC7BA}"/>
 </file>